--- a/docs/仕様/機能定義書-LMMVMV-API-02_30分値一覧取得API.xlsx
+++ b/docs/仕様/機能定義書-LMMVMV-API-02_30分値一覧取得API.xlsx
@@ -12014,7 +12014,7 @@
       <c r="P48" s="25"/>
       <c r="Q48" s="54"/>
       <c r="R48" s="134" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="S48" s="55"/>
       <c r="T48" s="55"/>
@@ -12125,7 +12125,7 @@
       <c r="P49" s="131"/>
       <c r="Q49" s="132"/>
       <c r="R49" s="134" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="S49" s="55"/>
       <c r="T49" s="55"/>
